--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27750332e5828b7f/שולחן העבודה/lyn_xml_validator_streamlit_v2/lyn_xml_validator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{7BEE02C9-DAD2-488B-9ECE-110FD122E3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{816BE4F3-02DC-494D-AFCD-E4FAE52F2FF3}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{7BEE02C9-DAD2-488B-9ECE-110FD122E3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{323FF458-B0A3-4E49-9A82-472EFE72C6B5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2307,7 +2307,7 @@
         <v>600</v>
       </c>
       <c r="I4">
-        <v>679369</v>
+        <v>655504</v>
       </c>
       <c r="J4" t="s">
         <v>23</v>
@@ -2964,7 +2964,7 @@
         <v>800</v>
       </c>
       <c r="I25">
-        <v>29963534</v>
+        <v>4192039</v>
       </c>
       <c r="J25" t="s">
         <v>119</v>
@@ -5617,10 +5617,10 @@
         <v>20</v>
       </c>
       <c r="H108">
-        <v>905</v>
+        <v>638</v>
       </c>
       <c r="I108">
-        <v>243228</v>
+        <v>133747</v>
       </c>
       <c r="J108" t="s">
         <v>77</v>
